--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487203_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487203_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0704</v>
+        <v>5.1622</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2623</v>
+        <v>6.4612</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1919</v>
+        <v>-1.2989</v>
       </c>
       <c r="G2" t="n">
         <v>2.5179</v>
@@ -610,13 +610,13 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3246</v>
+        <v>0.4164</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5315</v>
+        <v>-0.2697</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7931</v>
+        <v>0.6861</v>
       </c>
       <c r="V2" t="n">
         <v>1.842</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4101</v>
+        <v>2.5905</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3202</v>
+        <v>2.4204</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.1702</v>
       </c>
       <c r="G3" t="n">
         <v>3.2417</v>
@@ -688,13 +688,13 @@
         <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6736</v>
+        <v>-0.4931</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5803</v>
+        <v>-0.4802</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0129</v>
       </c>
       <c r="V3" t="n">
         <v>0.614</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0228</v>
+        <v>2.5235</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5337</v>
+        <v>1.0344</v>
       </c>
       <c r="F4" t="n">
         <v>1.489</v>
@@ -766,10 +766,10 @@
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.0321</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2796</v>
+        <v>-0.7789</v>
       </c>
       <c r="U4" t="n">
         <v>0.7469</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GONZALEZ RUIZ</t>
+          <t>D. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2098</v>
+        <v>0.3939</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0265</v>
+        <v>-1.5107</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1833</v>
+        <v>1.9046</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8622</v>
+        <v>0.9321</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3416</v>
+        <v>-0.1604</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5205</v>
+        <v>1.0924</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1057</v>
+        <v>-0.2293</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0414</v>
+        <v>-0.2536</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1471</v>
+        <v>0.0243</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9679</v>
+        <v>1.1614</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3002</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6676</v>
+        <v>1.0682</v>
       </c>
       <c r="P5" t="n">
-        <v>0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
         <v>0.193</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2736</v>
+        <v>-0.1365</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1322</v>
+        <v>-0.3163</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4059</v>
+        <v>0.1798</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5717</v>
+        <v>0.3704</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5717</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ALLAS MENESES</t>
+          <t>R. GONZALEZ RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0275</v>
+        <v>0.0234</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6108</v>
+        <v>-0.374</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5833</v>
+        <v>0.3974</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9321</v>
+        <v>0.8622</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1604</v>
+        <v>0.3416</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0924</v>
+        <v>0.5205</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2293</v>
+        <v>-0.1057</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2536</v>
+        <v>0.0414</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0243</v>
+        <v>-0.1471</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1614</v>
+        <v>0.9679</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.3002</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0682</v>
+        <v>0.6676</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.193</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5579</v>
+        <v>-0.46</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4164</v>
+        <v>-0.2683</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1415</v>
+        <v>-0.1917</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3704</v>
+        <v>-0.5717</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3704</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>C. POLANCO MERINO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8222</v>
+        <v>-0.6986</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.23</v>
+        <v>-0.0936</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4078</v>
+        <v>-0.605</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3396</v>
+        <v>-1.7834</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.2838</v>
+        <v>-1.0359</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9443</v>
+        <v>-0.7476</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4578</v>
+        <v>0.7869</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9462</v>
+        <v>1.3816</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4884</v>
+        <v>-0.5948</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8818</v>
+        <v>-2.5703</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.3377</v>
+        <v>-2.4175</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4559</v>
+        <v>-0.1528</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.0182</v>
+        <v>-0.579</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.7553</v>
+        <v>-1.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9518</v>
+        <v>-0.1781</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0556</v>
+        <v>-0.1361</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8963</v>
+        <v>-0.042</v>
       </c>
       <c r="V7" t="n">
-        <v>4.5838</v>
+        <v>1.842</v>
       </c>
       <c r="W7" t="n">
-        <v>3.9275</v>
+        <v>1.1857</v>
       </c>
       <c r="X7" t="n">
         <v>0.6562</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. POLANCO MERINO</t>
+          <t>P. FERNANDEZ MENDIGUCHIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.886</v>
+        <v>-1.0978</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0936</v>
+        <v>-0.4716</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7924</v>
+        <v>-0.6262</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7834</v>
+        <v>-0.8417</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0359</v>
+        <v>-0.0341</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7476</v>
+        <v>-0.8076</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7869</v>
+        <v>-0.2743</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3816</v>
+        <v>0.3933</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5948</v>
+        <v>-0.6676</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5703</v>
+        <v>-0.5674</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.4175</v>
+        <v>-0.4274</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1528</v>
+        <v>-0.14</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.579</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3511</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3655</v>
+        <v>-0.2561</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1361</v>
+        <v>-0.1973</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2294</v>
+        <v>-0.0588</v>
       </c>
       <c r="V8" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1857</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ MENDIGUCHIA</t>
+          <t>S. MARTINEZ ORTIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1444</v>
+        <v>-1.7093</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5718</v>
+        <v>-1.1569</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5727</v>
+        <v>-0.5523</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8417</v>
+        <v>2.3157</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0341</v>
+        <v>0.9369</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8076</v>
+        <v>1.3788</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2743</v>
+        <v>2.0558</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3933</v>
+        <v>1.7387</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6676</v>
+        <v>0.317</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5674</v>
+        <v>0.2599</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4274</v>
+        <v>-0.8018</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.14</v>
+        <v>1.0617</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3027</v>
+        <v>-0.388</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2974</v>
+        <v>-0.3176</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0053</v>
+        <v>-0.0704</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. MARTINEZ ORTIZ</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4509</v>
+        <v>-2.2667</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6576</v>
+        <v>-4.6305</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7933</v>
+        <v>2.3638</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3157</v>
+        <v>-2.3396</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9369</v>
+        <v>-4.2838</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3788</v>
+        <v>1.9443</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0558</v>
+        <v>-1.4578</v>
       </c>
       <c r="K10" t="n">
-        <v>1.7387</v>
+        <v>-1.9462</v>
       </c>
       <c r="L10" t="n">
-        <v>0.317</v>
+        <v>0.4884</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2599</v>
+        <v>-0.8818</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8018</v>
+        <v>-2.3377</v>
       </c>
       <c r="O10" t="n">
-        <v>1.0617</v>
+        <v>1.4559</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1231</v>
+        <v>-5.0182</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8951</v>
+        <v>-6.7553</v>
       </c>
       <c r="R10" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1296</v>
+        <v>0.5073</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8183</v>
+        <v>-0.345</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3114</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5138</v>
+        <v>4.5838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.9275</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5138</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0375</v>
+        <v>-3.5765</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3159</v>
+        <v>-2.0155</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7216</v>
+        <v>-1.561</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5077</v>
@@ -1312,13 +1312,13 @@
         <v>0.193</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4719</v>
+        <v>-0.0109</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1785</v>
+        <v>0.122</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2935</v>
+        <v>-0.1329</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2859</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.344599999999999</v>
+        <v>1.344600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3370000000000011</v>
+        <v>-0.3368000000000007</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6814</v>
+        <v>1.6816</v>
       </c>
       <c r="G12" t="n">
-        <v>9.399199999999999</v>
+        <v>9.3992</v>
       </c>
       <c r="H12" t="n">
         <v>-7.580300000000001</v>
@@ -1372,7 +1372,7 @@
         <v>11.0673</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.143700000000001</v>
+        <v>-6.1437</v>
       </c>
       <c r="N12" t="n">
         <v>-12.0556</v>
@@ -1390,13 +1390,13 @@
         <v>8.6854</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0312</v>
+        <v>-1.0311</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.9873</v>
+        <v>-2.9874</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9561</v>
+        <v>1.9564</v>
       </c>
       <c r="V12" t="n">
         <v>7.452500000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. QUINCY-JONES</t>
+          <t>E. GANDARILLAS GARMENDIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1828</v>
+        <v>3.09</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6826</v>
+        <v>0.2887</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5002</v>
+        <v>2.8014</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5218</v>
+        <v>-0.5199</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5636</v>
+        <v>0.0641</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0418</v>
+        <v>-0.5841</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4152</v>
+        <v>1.3274</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0178</v>
+        <v>0.6519</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6026</v>
+        <v>0.6755</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8934</v>
+        <v>-1.8473</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4542</v>
+        <v>-0.5878</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4391</v>
+        <v>-1.2596</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8951</v>
+        <v>2.3161</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R13" t="n">
-        <v>2.8951</v>
+        <v>3.4741</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2797</v>
+        <v>0.1887</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0185</v>
+        <v>-0.4524</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2981</v>
+        <v>0.6411</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.5138</v>
+        <v>1.1052</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2859</v>
+        <v>0.5717</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7997</v>
+        <v>0.5334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. GANDARILLAS GARMENDIA</t>
+          <t>A. QUINCY-JONES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1623</v>
+        <v>2.8414</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6126</v>
+        <v>1.5825</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7749</v>
+        <v>1.2589</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5199</v>
+        <v>0.5218</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0641</v>
+        <v>1.5636</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5841</v>
+        <v>-1.0418</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3274</v>
+        <v>1.4152</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6519</v>
+        <v>2.0178</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6755</v>
+        <v>-0.6026</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8473</v>
+        <v>-0.8934</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5878</v>
+        <v>-0.4542</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2596</v>
+        <v>-0.4391</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3161</v>
+        <v>2.8951</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.4741</v>
+        <v>2.8951</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.739</v>
+        <v>0.9383</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3537</v>
+        <v>-0.1186</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6147</v>
+        <v>1.0569</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1052</v>
+        <v>-1.5138</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5717</v>
+        <v>0.2859</v>
       </c>
       <c r="X14" t="n">
-        <v>0.5334</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>L. MAESTRO STEELE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7129</v>
+        <v>1.5411</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0314</v>
+        <v>0.4386</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3186</v>
+        <v>1.1025</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9522</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2099</v>
+        <v>4.0746</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.162</v>
+        <v>-3.9856</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4088</v>
+        <v>1.9636</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0764</v>
+        <v>5.2367</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6676</v>
+        <v>-3.273</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3609</v>
+        <v>-1.8747</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1335</v>
+        <v>-1.1621</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4944</v>
+        <v>-0.7126</v>
       </c>
       <c r="P15" t="n">
-        <v>1.158</v>
+        <v>2.7021</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="R15" t="n">
-        <v>1.158</v>
+        <v>2.8951</v>
       </c>
       <c r="S15" t="n">
-        <v>0.507</v>
+        <v>0.1431</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6227</v>
+        <v>-0.6758</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1157</v>
+        <v>0.8189</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.393</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.7368</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. MAESTRO STEELE</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3986</v>
+        <v>0.4392</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0621</v>
+        <v>0.731</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4607</v>
+        <v>-0.2918</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.9522</v>
       </c>
       <c r="H16" t="n">
-        <v>4.0746</v>
+        <v>1.2099</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.9856</v>
+        <v>-2.162</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9636</v>
+        <v>0.4088</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2367</v>
+        <v>1.0764</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.273</v>
+        <v>-0.6676</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8747</v>
+        <v>-1.3609</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1621</v>
+        <v>0.1335</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7126</v>
+        <v>-1.4944</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7021</v>
+        <v>1.158</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8951</v>
+        <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9994</v>
+        <v>0.2333</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1765</v>
+        <v>0.3222</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1771</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.393</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1495</v>
+        <v>-0.49</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7258</v>
+        <v>-0.4126</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5763</v>
+        <v>-0.0774</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.2398</v>
+        <v>-1.8381</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.273</v>
+        <v>1.9519</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9668</v>
+        <v>-3.79</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.8322</v>
+        <v>0.1963</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.8322</v>
+        <v>2.1991</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-2.0028</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4076</v>
+        <v>-2.0345</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4408</v>
+        <v>-0.2473</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9668</v>
+        <v>-1.7872</v>
       </c>
       <c r="P17" t="n">
         <v>1.7371</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7021</v>
+        <v>3.8602</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0251</v>
+        <v>-0.3467</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4574</v>
+        <v>-0.5714</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4323</v>
+        <v>0.2247</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3281</v>
+        <v>-0.0422</v>
       </c>
       <c r="W17" t="n">
-        <v>0.614</v>
+        <v>2.0856</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3357</v>
+        <v>-1.0353</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2206</v>
+        <v>0.0799</v>
       </c>
       <c r="F18" t="n">
         <v>-1.1151</v>
@@ -1858,10 +1858,10 @@
         <v>0.772</v>
       </c>
       <c r="S18" t="n">
-        <v>-0</v>
+        <v>0.3004</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2974</v>
+        <v>0.003</v>
       </c>
       <c r="U18" t="n">
         <v>0.2974</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5248</v>
+        <v>-1.5097</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3138</v>
+        <v>-2.3267</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2109</v>
+        <v>0.8169</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8381</v>
+        <v>-3.2398</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9519</v>
+        <v>-2.273</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.79</v>
+        <v>-0.9668</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1963</v>
+        <v>-1.8322</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1991</v>
+        <v>-1.8322</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0028</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0345</v>
+        <v>-1.4076</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2473</v>
+        <v>-0.4408</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7872</v>
+        <v>-0.9668</v>
       </c>
       <c r="P19" t="n">
         <v>1.7371</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1231</v>
+        <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>3.8602</v>
+        <v>2.7021</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3815</v>
+        <v>-0.3351</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4726</v>
+        <v>-0.1434</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0912</v>
+        <v>-0.1917</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0422</v>
+        <v>0.3281</v>
       </c>
       <c r="W19" t="n">
-        <v>2.0856</v>
+        <v>0.614</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1278</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5989</v>
+        <v>-2.1727</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6405999999999999</v>
+        <v>-0.3608</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2395</v>
+        <v>-1.8118</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5148</v>
@@ -2014,13 +2014,13 @@
         <v>2.8951</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1435</v>
+        <v>0.5698</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9453</v>
+        <v>-0.0561</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1983</v>
+        <v>0.6259</v>
       </c>
       <c r="V20" t="n">
         <v>-1.9647</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1923</v>
+        <v>-2.7135</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1012</v>
+        <v>-1.702</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0912</v>
+        <v>-1.0115</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1881</v>
@@ -2092,13 +2092,13 @@
         <v>2.5091</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1957</v>
+        <v>0.6745</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3372</v>
+        <v>-0.2637</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8586</v>
+        <v>0.9382</v>
       </c>
       <c r="V21" t="n">
         <v>-2.621</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3446</v>
+        <v>-0.009500000000000064</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6815</v>
+        <v>-1.6814</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3368</v>
+        <v>1.672099999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-9.3992</v>
@@ -2170,13 +2170,13 @@
         <v>23.1608</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0311</v>
+        <v>2.3663</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.9561</v>
+        <v>-1.9562</v>
       </c>
       <c r="U22" t="n">
-        <v>2.9874</v>
+        <v>4.3225</v>
       </c>
       <c r="V22" t="n">
         <v>-7.452199999999999</v>
